--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="145">
   <si>
     <t>DateTime</t>
   </si>
@@ -457,6 +457,9 @@
   <si>
     <t>Cleaned weeds and some sticks off grate</t>
   </si>
+  <si>
+    <t>Measured about 0.75" going over spillway</t>
+  </si>
 </sst>
 </file>
 
@@ -779,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1198"/>
+  <dimension ref="A1:E1209"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -16492,6 +16495,145 @@
         <v>1.58</v>
       </c>
     </row>
+    <row r="1199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1199" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1199" s="1">
+        <v>46242.445138888892</v>
+      </c>
+      <c r="C1199" s="2">
+        <v>1.58</v>
+      </c>
+      <c r="D1199">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1200" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1200" s="1">
+        <v>46243.5</v>
+      </c>
+      <c r="C1200" s="2">
+        <v>1.57</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1201" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1201" s="1">
+        <v>46244.415277777778</v>
+      </c>
+      <c r="C1201" s="2">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1202" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1202" s="1">
+        <v>46245.459722222222</v>
+      </c>
+      <c r="C1202" s="2">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1203" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1203" s="1">
+        <v>46246.444444444445</v>
+      </c>
+      <c r="C1203" s="2">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1204" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1204" s="1">
+        <v>46247.427083333336</v>
+      </c>
+      <c r="C1204" s="2">
+        <v>1.55</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1205" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1205" s="1">
+        <v>46248.638194444444</v>
+      </c>
+      <c r="C1205" s="2">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1206" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1206" s="1">
+        <v>46249.502083333333</v>
+      </c>
+      <c r="C1206" s="2">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1207" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1207" s="1">
+        <v>46250.520833333336</v>
+      </c>
+      <c r="C1207" s="2">
+        <v>1.56</v>
+      </c>
+      <c r="D1207">
+        <v>0.04</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1208" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1208" s="1">
+        <v>46251.413194444445</v>
+      </c>
+      <c r="C1208" s="2">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1209" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1209" s="1">
+        <v>46252.544444444444</v>
+      </c>
+      <c r="C1209" s="2">
+        <v>1.54</v>
+      </c>
+      <c r="D1209">
+        <v>0.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="148">
   <si>
     <t>DateTime</t>
   </si>
@@ -460,6 +460,15 @@
   <si>
     <t>Measured about 0.75" going over spillway</t>
   </si>
+  <si>
+    <t>Cleared weeds off spillway after reading</t>
+  </si>
+  <si>
+    <t>Double-checked reading</t>
+  </si>
+  <si>
+    <t>Water barely trickling over spillway; Double-checked reading</t>
+  </si>
 </sst>
 </file>
 
@@ -782,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1209"/>
+  <dimension ref="A1:E1228"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -16634,6 +16643,248 @@
         <v>0.08</v>
       </c>
     </row>
+    <row r="1210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1210" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1210" s="1">
+        <v>46253.595833333333</v>
+      </c>
+      <c r="C1210" s="2">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1211" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1211" s="1">
+        <v>46254.5</v>
+      </c>
+      <c r="C1211" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1212" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1212" s="1">
+        <v>46255.5</v>
+      </c>
+      <c r="C1212" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1213" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1213" s="1">
+        <v>46256.5</v>
+      </c>
+      <c r="C1213" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1214" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1214" s="1">
+        <v>46257.5</v>
+      </c>
+      <c r="C1214" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1215" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1215" s="1">
+        <v>46258.474305555559</v>
+      </c>
+      <c r="C1215" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1216" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1216" s="1">
+        <v>46259.719444444447</v>
+      </c>
+      <c r="C1216" s="2">
+        <v>1.48</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1217" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1217" s="1">
+        <v>46260.584027777775</v>
+      </c>
+      <c r="C1217" s="2">
+        <v>1.53</v>
+      </c>
+      <c r="D1217">
+        <v>0.19</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1218" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1218" s="1">
+        <v>46261.38958333333</v>
+      </c>
+      <c r="C1218" s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1219" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1219" s="1">
+        <v>46262.451388888891</v>
+      </c>
+      <c r="C1219" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1220" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1220" s="1">
+        <v>46263.490277777775</v>
+      </c>
+      <c r="C1220" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="D1220">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1221" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1221" s="1">
+        <v>46264.45208333333</v>
+      </c>
+      <c r="C1221" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1222" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1222" s="1">
+        <v>46265.486111111109</v>
+      </c>
+      <c r="C1222" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="D1222">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1223" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1223" s="1">
+        <v>46266.407638888886</v>
+      </c>
+      <c r="C1223" s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1224" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1224" s="1">
+        <v>46267.606944444444</v>
+      </c>
+      <c r="C1224" s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1225" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1225" s="1">
+        <v>46268.597222222219</v>
+      </c>
+      <c r="C1225" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1226" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1226" s="1">
+        <v>46269.625</v>
+      </c>
+      <c r="C1226" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="D1226">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1227" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1227" s="1">
+        <v>46270.523611111108</v>
+      </c>
+      <c r="C1227" s="2">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1228" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1228" s="1">
+        <v>46271.557638888888</v>
+      </c>
+      <c r="C1228" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
+++ b/portfolio/posts/_data/Flynn_Dam_Heights.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="153">
   <si>
     <t>DateTime</t>
   </si>
@@ -469,6 +469,21 @@
   <si>
     <t>Water barely trickling over spillway; Double-checked reading</t>
   </si>
+  <si>
+    <t>Cleaned grate after the reading; water barely trickling over spillway</t>
+  </si>
+  <si>
+    <t>Very windy right towards dam</t>
+  </si>
+  <si>
+    <t>Kevin took reading</t>
+  </si>
+  <si>
+    <t>dammed up with leaves</t>
+  </si>
+  <si>
+    <t>cleaned leaves prior to reading</t>
+  </si>
 </sst>
 </file>
 
@@ -791,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1228"/>
+  <dimension ref="A1:E1265"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -16885,6 +16900,512 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="1229" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1229" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1229" s="1">
+        <v>46272.5</v>
+      </c>
+      <c r="C1229" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1230" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1230" s="1">
+        <v>46273.550694444442</v>
+      </c>
+      <c r="C1230" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="D1230">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1231" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1231" s="1">
+        <v>46274.5</v>
+      </c>
+      <c r="C1231" s="2">
+        <v>1.53</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1232" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1232" s="1">
+        <v>46275.5</v>
+      </c>
+      <c r="C1232" s="2">
+        <v>1.54</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1233" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1233" s="1">
+        <v>46276.5</v>
+      </c>
+      <c r="C1233" s="2">
+        <v>1.49</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1234" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1234" s="1">
+        <v>46277.5</v>
+      </c>
+      <c r="C1234" s="2">
+        <v>1.54</v>
+      </c>
+      <c r="D1234">
+        <v>0.19</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1235" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1235" s="1">
+        <v>46278.5</v>
+      </c>
+      <c r="C1235" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1236" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1236" s="1">
+        <v>46279.50277777778</v>
+      </c>
+      <c r="C1236" s="2">
+        <v>1.48</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1237" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1237" s="1">
+        <v>46280.429166666669</v>
+      </c>
+      <c r="C1237" s="2">
+        <v>1.56</v>
+      </c>
+      <c r="D1237">
+        <v>0.66</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1238" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1238" s="1">
+        <v>46281.510416666664</v>
+      </c>
+      <c r="C1238" s="2">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1239" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1239" s="1">
+        <v>46282.466666666667</v>
+      </c>
+      <c r="C1239" s="2">
+        <v>1.54</v>
+      </c>
+      <c r="D1239">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1240" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1240" s="1">
+        <v>46283.624305555553</v>
+      </c>
+      <c r="C1240" s="2">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1241" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1241" s="1">
+        <v>46284.509722222225</v>
+      </c>
+      <c r="C1241" s="2">
+        <v>1.53</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1242" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1242" s="1">
+        <v>46285.727777777778</v>
+      </c>
+      <c r="C1242" s="2">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1243" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1243" s="1">
+        <v>46286.524305555555</v>
+      </c>
+      <c r="C1243" s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1244" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1244" s="1">
+        <v>46287.418749999997</v>
+      </c>
+      <c r="C1244" s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1245" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1245" s="1">
+        <v>46288.5</v>
+      </c>
+      <c r="C1245" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1246" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1246" s="1">
+        <v>46289.5</v>
+      </c>
+      <c r="C1246" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1247" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1247" s="1">
+        <v>46290.5</v>
+      </c>
+      <c r="C1247" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1248" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1248" s="1">
+        <v>46291.5</v>
+      </c>
+      <c r="C1248" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1249" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1249" s="1">
+        <v>46292.5</v>
+      </c>
+      <c r="C1249" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="D1249">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1250" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1250" s="1">
+        <v>46293.438194444447</v>
+      </c>
+      <c r="C1250" s="2">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1251" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1251" s="1">
+        <v>46294.5</v>
+      </c>
+      <c r="C1251" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="E1251" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1252" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1252" s="1">
+        <v>46295.581250000003</v>
+      </c>
+      <c r="C1252" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="D1252">
+        <v>0.05</v>
+      </c>
+      <c r="E1252" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1253" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1253" s="1">
+        <v>46296.572222222225</v>
+      </c>
+      <c r="C1253" s="2">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1254" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1254" s="1">
+        <v>46297.524305555555</v>
+      </c>
+      <c r="C1254" s="2">
+        <v>1.53</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1255" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1255" s="1">
+        <v>46298.51666666667</v>
+      </c>
+      <c r="C1255" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1256" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1256" s="1">
+        <v>46299.472222222219</v>
+      </c>
+      <c r="C1256" s="2">
+        <v>1.56</v>
+      </c>
+      <c r="D1256">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1257" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1257" s="1">
+        <v>46300.5</v>
+      </c>
+      <c r="C1257" s="2">
+        <v>1.55</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1258" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1258" s="1">
+        <v>46301.518750000003</v>
+      </c>
+      <c r="C1258" s="2">
+        <v>1.56</v>
+      </c>
+      <c r="D1258">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1259" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1259" s="1">
+        <v>46302.506249999999</v>
+      </c>
+      <c r="C1259" s="2">
+        <v>1.58</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1260" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1260" s="1">
+        <v>46303.407638888886</v>
+      </c>
+      <c r="C1260" s="2">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1261" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1261" s="1">
+        <v>46304.427083333336</v>
+      </c>
+      <c r="C1261" s="2">
+        <v>1.54</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1262" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1262" s="1">
+        <v>46305.429166666669</v>
+      </c>
+      <c r="C1262" s="2">
+        <v>1.53</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1263" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1263" s="1">
+        <v>46306.552777777775</v>
+      </c>
+      <c r="C1263" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1264" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1264" s="1">
+        <v>46307.505555555559</v>
+      </c>
+      <c r="C1264" s="2">
+        <v>1.52</v>
+      </c>
+      <c r="E1264" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1265" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1265" s="1">
+        <v>46308.600694444445</v>
+      </c>
+      <c r="C1265" s="2">
+        <v>1.54</v>
+      </c>
+      <c r="D1265">
+        <v>0.03</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>152</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
